--- a/datos/fomrato nuevo api jaboneria/EJEMPLO_AcuerdoCompleto_Directo.xlsx
+++ b/datos/fomrato nuevo api jaboneria/EJEMPLO_AcuerdoCompleto_Directo.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DiegoAntonioConstant\Desktop\TrazabilidadSeguimiento\datos\fomrato nuevo api jaboneria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4D42F7-3E19-4F01-A5F1-B77A176046AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA04CC49-495A-4AA7-8D07-1F2CCD9505A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ACUERDO COMPLETO" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -67,9 +72,6 @@
     <t>CANTIDAD</t>
   </si>
   <si>
-    <t>JAVIER MALDONADO</t>
-  </si>
-  <si>
     <t>ACOSTA SANTAMARIA EDGAR PATRICIO</t>
   </si>
   <si>
@@ -92,6 +94,9 @@
   </si>
   <si>
     <t>Diego Constante</t>
+  </si>
+  <si>
+    <t>QUITO</t>
   </si>
 </sst>
 </file>
@@ -551,22 +556,22 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
       </c>
       <c r="H3">
         <v>180</v>
@@ -601,22 +606,22 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
       <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>21</v>
-      </c>
-      <c r="G4" t="s">
-        <v>22</v>
       </c>
       <c r="H4">
         <v>90</v>
